--- a/ig/mc-changes/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4916" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4925" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T12:40:41+00:00</t>
+    <t>2023-05-09T14:30:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -621,10 +621,13 @@
 </t>
   </si>
   <si>
-    <t>[DR] : certificat</t>
+    <t>[DR] : certificat.</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les certificats utilisés par les professionnels et les structures comme moyen d'identification.</t>
+  </si>
+  <si>
+    <t>Données descriptives du moyen d’identification par certificat.</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-pharmacy-licence</t>
@@ -637,10 +640,13 @@
 </t>
   </si>
   <si>
-    <t>numeroLicence</t>
-  </si>
-  <si>
     <t>Numéro de la licence d'exploitation d’une officine.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la licence d’exploitation d’une officine.</t>
+  </si>
+  <si>
+    <t>Synonyme : numeroLicence</t>
   </si>
   <si>
     <t>Organization.modifierExtension</t>
@@ -838,7 +844,7 @@
 </t>
   </si>
   <si>
-    <t>isActive</t>
+    <t>La ressource est-elle active? active | inactive</t>
   </si>
   <si>
     <t>Whether the organization's record is still in active use.</t>
@@ -889,11 +895,12 @@
     <t>organizationType</t>
   </si>
   <si>
-    <t>Type de strcuture</t>
-  </si>
-  <si>
-    <t>Entitité Juridique : LEGAL-ENTITY; 
+    <t>Type de structure 
+Entité Juridique : LEGAL-ENTITY; 
 Entité Géographique : GEOGRAPHICAL-ENTITY</t>
+  </si>
+  <si>
+    <t>typeStructure</t>
   </si>
   <si>
     <t>http://interopsante.org/fhir/ValueSet/fr-organization-type</t>
@@ -1183,6 +1190,9 @@
 Plus précisément, on distingue le code APET pour les EG.</t>
   </si>
   <si>
+    <t>Synonyme : codeAPEN</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
   </si>
   <si>
@@ -1192,7 +1202,10 @@
     <t>statutJuridiqueINSEE</t>
   </si>
   <si>
-    <t>Statut juridique FINESS qui caracterise la situation juridique de la personne morale</t>
+    <t>Statut juridique FINESS qui caracterise la situation juridique de la personne morale.</t>
+  </si>
+  <si>
+    <t>Synonyme : statutJuridiqueINSEE</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
@@ -1204,7 +1217,10 @@
     <t>sphParticipation</t>
   </si>
   <si>
-    <t>Modalités de participation au service public hospitalier</t>
+    <t>Modalités de participation au service public hospitalier.</t>
+  </si>
+  <si>
+    <t>Synonyme : modaliteParticipationSPH</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J162-ESPIC-RASS/FHIR/JDV-J162-ESPIC-RASS</t>
@@ -1213,13 +1229,13 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>raisonSociale</t>
+    <t>Raison sociale de la structure.</t>
   </si>
   <si>
     <t>A name associated with the organization.</t>
   </si>
   <si>
-    <t>Raison Sociale de la structure</t>
+    <t>Synonyme : raisonSociale, dénomination</t>
   </si>
   <si>
     <t>Need to use the name as the label of the organization.</t>
@@ -1228,13 +1244,13 @@
     <t>Organization.alias</t>
   </si>
   <si>
-    <t>complementRaisonSociale</t>
+    <t>Enseigne commerciale de la structure.</t>
   </si>
   <si>
     <t>A list of alternate names that the organization is known as, or was known as in the past.</t>
   </si>
   <si>
-    <t>Enseigne commerciale de la structure</t>
+    <t>Synonyme : complementRaisonSociale</t>
   </si>
   <si>
     <t>Over time locations and organizations go through many changes and can be known by different names.
@@ -1248,13 +1264,13 @@
 </t>
   </si>
   <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
+    <t>Différentes instances pour les téléphones, la télécopie et l’adresse mail.</t>
   </si>
   <si>
     <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
-    <t>Différentes instances pour les téléphones, la télécopie et l’adresse mail.</t>
+    <t>The use code 'home' is not to be used. Note that these contacts are not the contact details of people who are employed by or represent the organization, but official contacts for the organization itself.</t>
   </si>
   <si>
     <t>Human contact for the organization.</t>
@@ -1396,13 +1412,13 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">adresseEJ : Adresse géopostale de l'entité juridique ou adresseEG : Adresse(s) géopostale(s) de l'entité géographique </t>
+  </si>
+  <si>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
+  </si>
+  <si>
     <t>adresse</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adresseEJ : Adresse géopostale de l'entité juridique ou adresseEG : Adresse(s) géopostale(s) de l'entité géographique </t>
   </si>
   <si>
     <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
@@ -1419,7 +1435,7 @@
 </t>
   </si>
   <si>
-    <t>Référence vers la structure de rattachement (lien EG/ EJ)</t>
+    <t>Référence vers la structure de rattachement (lien EG/ EJ).</t>
   </si>
   <si>
     <t>The organization of which this organization forms a part.</t>
@@ -1515,13 +1531,13 @@
 </t>
   </si>
   <si>
-    <t>contact</t>
+    <t>Point de contact.</t>
   </si>
   <si>
     <t>Contact for the organization for a certain purpose.</t>
   </si>
   <si>
-    <t>Point(s) de contact</t>
+    <t>Personne ou service agissant comme point de contact auprès d'une autre personne ou d'un autre service.</t>
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
@@ -1593,6 +1609,9 @@
     <t>Organization.contact.telecom</t>
   </si>
   <si>
+    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
+  </si>
+  <si>
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
@@ -1663,10 +1682,14 @@
     <t>type</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>Valeurs possibles :
+    <t>Type de boîte aux lettres.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : typeBAL 
+Valeurs possibles :
 ORG pour une BAL organisationnelle;
 APP pour une BAL applicative;
 PER pour une BAL personnelle, rattachée à une personne physique</t>
@@ -1684,7 +1707,7 @@
     <t>Organization.contact.telecom.extension.extension.extension</t>
   </si>
   <si>
-    <t>An Extension</t>
+    <t>Extension</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
@@ -1714,7 +1737,10 @@
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
   </si>
   <si>
-    <t>Description fonctionnelle de la boîte aux lettres</t>
+    <t>Description fonctionnelle de la boîte aux lettres.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : description</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
@@ -1735,7 +1761,10 @@
     <t>responsible</t>
   </si>
   <si>
-    <t>[DR] : mailBoxMSSresponsable</t>
+    <t>[DR] : responsable de la BAL MSS.</t>
+  </si>
+  <si>
+    <t>Synonyme : mailBoxMSSresponsable</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
@@ -1759,6 +1788,9 @@
     <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
   </si>
   <si>
+    <t>Synonyme MOS : serviceRattachement</t>
+  </si>
+  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
   </si>
   <si>
@@ -1777,7 +1809,10 @@
     <t>phone</t>
   </si>
   <si>
-    <t>[DR] : mailBoxMSS.phone</t>
+    <t>[DR] : Coordonnées téléphoniques spécifiques à l’usage de la BAL MSS.</t>
+  </si>
+  <si>
+    <t>Synonyme : mailBoxMSS.phone</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.id</t>
@@ -1799,7 +1834,10 @@
   </si>
   <si>
     <t>Indicateur d’acceptation de la dématérialisation (ou « Zéro papier »). - O : Dématérialisation acceptée 
-- N : Dématérialisation refusée</t>
+- N : Dématérialisation refusée.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : dematerialisation</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
@@ -1822,6 +1860,9 @@
   <si>
     <t>Indicateur liste rouge. O: Boîte aux lettres en liste rouge;
 N: La boîte aux lettres peut être publiée</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : listeRouge</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.id</t>
@@ -4457,7 +4498,9 @@
       <c r="M22" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N22" s="2"/>
+      <c r="N22" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>71</v>
@@ -4523,13 +4566,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>71</v>
@@ -4551,15 +4594,17 @@
         <v>71</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>71</v>
@@ -4625,10 +4670,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4654,16 +4699,16 @@
         <v>123</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>71</v>
@@ -4712,7 +4757,7 @@
         <v>129</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>72</v>
@@ -4729,10 +4774,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4755,19 +4800,19 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>71</v>
@@ -4816,7 +4861,7 @@
         <v>71</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>72</v>
@@ -4825,7 +4870,7 @@
         <v>73</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>91</v>
@@ -4833,10 +4878,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4933,10 +4978,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5035,10 +5080,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5064,23 +5109,23 @@
         <v>99</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>71</v>
@@ -5098,13 +5143,13 @@
         <v>71</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>71</v>
@@ -5122,7 +5167,7 @@
         <v>71</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>72</v>
@@ -5139,10 +5184,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5165,19 +5210,19 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>71</v>
@@ -5202,13 +5247,13 @@
         <v>71</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>71</v>
@@ -5226,7 +5271,7 @@
         <v>71</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>72</v>
@@ -5243,10 +5288,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5272,16 +5317,16 @@
         <v>93</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>71</v>
@@ -5294,7 +5339,7 @@
         <v>71</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>71</v>
@@ -5330,7 +5375,7 @@
         <v>71</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>72</v>
@@ -5347,10 +5392,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5376,13 +5421,13 @@
         <v>146</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5396,7 +5441,7 @@
         <v>71</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>71</v>
@@ -5432,7 +5477,7 @@
         <v>71</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>72</v>
@@ -5449,10 +5494,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5478,13 +5523,13 @@
         <v>163</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5534,7 +5579,7 @@
         <v>71</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>72</v>
@@ -5546,15 +5591,15 @@
         <v>90</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5577,16 +5622,16 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5636,7 +5681,7 @@
         <v>71</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>72</v>
@@ -5648,15 +5693,15 @@
         <v>90</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5679,70 +5724,70 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q34" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="R34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="P34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q34" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="R34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>72</v>
@@ -5759,10 +5804,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5785,19 +5830,19 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>71</v>
@@ -5822,19 +5867,19 @@
         <v>71</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -5844,7 +5889,7 @@
         <v>129</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>72</v>
@@ -5861,13 +5906,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>71</v>
@@ -5889,19 +5934,19 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>71</v>
@@ -5926,13 +5971,13 @@
         <v>71</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>71</v>
@@ -5950,7 +5995,7 @@
         <v>71</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>72</v>
@@ -5967,10 +6012,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6067,10 +6112,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6169,10 +6214,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6195,19 +6240,19 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>71</v>
@@ -6256,7 +6301,7 @@
         <v>71</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>72</v>
@@ -6273,10 +6318,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6373,10 +6418,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6475,10 +6520,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6504,29 +6549,29 @@
         <v>93</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>71</v>
@@ -6562,7 +6607,7 @@
         <v>71</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>72</v>
@@ -6579,10 +6624,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6608,13 +6653,13 @@
         <v>146</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6664,7 +6709,7 @@
         <v>71</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>72</v>
@@ -6681,10 +6726,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6710,16 +6755,16 @@
         <v>99</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>71</v>
@@ -6768,7 +6813,7 @@
         <v>71</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>72</v>
@@ -6785,10 +6830,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6814,16 +6859,16 @@
         <v>146</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>71</v>
@@ -6872,7 +6917,7 @@
         <v>71</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>72</v>
@@ -6889,10 +6934,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6915,19 +6960,19 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>71</v>
@@ -6976,7 +7021,7 @@
         <v>71</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>72</v>
@@ -6993,10 +7038,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7022,16 +7067,16 @@
         <v>146</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>71</v>
@@ -7080,7 +7125,7 @@
         <v>71</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>72</v>
@@ -7097,13 +7142,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>71</v>
@@ -7125,19 +7170,19 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>71</v>
@@ -7162,13 +7207,13 @@
         <v>71</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>71</v>
@@ -7186,7 +7231,7 @@
         <v>71</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>72</v>
@@ -7203,10 +7248,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7303,10 +7348,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7405,10 +7450,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7431,19 +7476,19 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>71</v>
@@ -7492,7 +7537,7 @@
         <v>71</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>72</v>
@@ -7509,10 +7554,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7609,10 +7654,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7711,10 +7756,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7740,29 +7785,29 @@
         <v>93</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>71</v>
@@ -7798,7 +7843,7 @@
         <v>71</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>72</v>
@@ -7815,10 +7860,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7844,13 +7889,13 @@
         <v>146</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7900,7 +7945,7 @@
         <v>71</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>72</v>
@@ -7917,10 +7962,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7946,16 +7991,16 @@
         <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>71</v>
@@ -8004,7 +8049,7 @@
         <v>71</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>72</v>
@@ -8021,10 +8066,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8050,16 +8095,16 @@
         <v>146</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>71</v>
@@ -8108,7 +8153,7 @@
         <v>71</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>72</v>
@@ -8125,10 +8170,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8151,19 +8196,19 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>71</v>
@@ -8212,7 +8257,7 @@
         <v>71</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>72</v>
@@ -8229,10 +8274,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8258,16 +8303,16 @@
         <v>146</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>71</v>
@@ -8316,7 +8361,7 @@
         <v>71</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>72</v>
@@ -8333,13 +8378,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>71</v>
@@ -8361,19 +8406,19 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>71</v>
@@ -8398,13 +8443,13 @@
         <v>71</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>71</v>
@@ -8422,7 +8467,7 @@
         <v>71</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>72</v>
@@ -8439,10 +8484,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8539,10 +8584,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8641,10 +8686,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8667,19 +8712,19 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>71</v>
@@ -8728,7 +8773,7 @@
         <v>71</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>72</v>
@@ -8745,10 +8790,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8845,10 +8890,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8947,10 +8992,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8976,23 +9021,23 @@
         <v>93</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>71</v>
@@ -9034,7 +9079,7 @@
         <v>71</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>72</v>
@@ -9051,10 +9096,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9080,13 +9125,13 @@
         <v>146</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9136,7 +9181,7 @@
         <v>71</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>72</v>
@@ -9153,10 +9198,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9182,16 +9227,16 @@
         <v>99</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>71</v>
@@ -9240,7 +9285,7 @@
         <v>71</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>72</v>
@@ -9257,10 +9302,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9286,16 +9331,16 @@
         <v>146</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>71</v>
@@ -9344,7 +9389,7 @@
         <v>71</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>72</v>
@@ -9361,10 +9406,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9387,19 +9432,19 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>71</v>
@@ -9448,7 +9493,7 @@
         <v>71</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>72</v>
@@ -9465,10 +9510,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9494,16 +9539,16 @@
         <v>146</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>71</v>
@@ -9552,7 +9597,7 @@
         <v>71</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>72</v>
@@ -9569,13 +9614,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>71</v>
@@ -9597,19 +9642,19 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>270</v>
+        <v>377</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>71</v>
@@ -9634,11 +9679,11 @@
         <v>71</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>71</v>
@@ -9656,7 +9701,7 @@
         <v>71</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>72</v>
@@ -9673,13 +9718,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>71</v>
@@ -9701,19 +9746,19 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>270</v>
+        <v>382</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>71</v>
@@ -9738,11 +9783,11 @@
         <v>71</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>71</v>
@@ -9760,7 +9805,7 @@
         <v>71</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>72</v>
@@ -9777,13 +9822,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>71</v>
@@ -9805,19 +9850,19 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>270</v>
+        <v>387</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>71</v>
@@ -9842,11 +9887,11 @@
         <v>71</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>71</v>
@@ -9864,7 +9909,7 @@
         <v>71</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>72</v>
@@ -9881,10 +9926,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9910,16 +9955,16 @@
         <v>146</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>71</v>
@@ -9968,7 +10013,7 @@
         <v>71</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>72</v>
@@ -9977,7 +10022,7 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>91</v>
@@ -9985,10 +10030,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10014,16 +10059,16 @@
         <v>146</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>71</v>
@@ -10072,7 +10117,7 @@
         <v>71</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>72</v>
@@ -10089,10 +10134,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10115,19 +10160,19 @@
         <v>71</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>71</v>
@@ -10176,7 +10221,7 @@
         <v>71</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>72</v>
@@ -10185,18 +10230,18 @@
         <v>73</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10293,10 +10338,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10395,13 +10440,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>122</v>
@@ -10423,10 +10468,10 @@
         <v>71</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>136</v>
@@ -10499,10 +10544,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10528,13 +10573,13 @@
         <v>99</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10560,13 +10605,13 @@
         <v>71</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>71</v>
@@ -10584,7 +10629,7 @@
         <v>71</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>72</v>
@@ -10593,7 +10638,7 @@
         <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>91</v>
@@ -10601,10 +10646,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10630,16 +10675,16 @@
         <v>146</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>71</v>
@@ -10688,7 +10733,7 @@
         <v>71</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>72</v>
@@ -10705,10 +10750,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10734,16 +10779,16 @@
         <v>99</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>71</v>
@@ -10768,13 +10813,13 @@
         <v>71</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>71</v>
@@ -10792,7 +10837,7 @@
         <v>71</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>72</v>
@@ -10809,10 +10854,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10835,16 +10880,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10894,7 +10939,7 @@
         <v>71</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>72</v>
@@ -10911,10 +10956,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10940,13 +10985,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10996,7 +11041,7 @@
         <v>71</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>72</v>
@@ -11008,15 +11053,15 @@
         <v>90</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11039,19 +11084,19 @@
         <v>71</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>71</v>
@@ -11100,7 +11145,7 @@
         <v>71</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>72</v>
@@ -11112,15 +11157,15 @@
         <v>90</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11143,19 +11188,19 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>71</v>
@@ -11204,7 +11249,7 @@
         <v>71</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>72</v>
@@ -11216,15 +11261,15 @@
         <v>90</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11321,10 +11366,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11423,10 +11468,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11452,13 +11497,13 @@
         <v>146</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11508,7 +11553,7 @@
         <v>71</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>72</v>
@@ -11517,7 +11562,7 @@
         <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>91</v>
@@ -11525,10 +11570,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11554,13 +11599,13 @@
         <v>93</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11586,13 +11631,13 @@
         <v>71</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>71</v>
@@ -11610,7 +11655,7 @@
         <v>71</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>72</v>
@@ -11627,10 +11672,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11653,16 +11698,16 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11712,7 +11757,7 @@
         <v>71</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>72</v>
@@ -11729,10 +11774,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11758,13 +11803,13 @@
         <v>146</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11814,7 +11859,7 @@
         <v>71</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>72</v>
@@ -11831,10 +11876,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11857,19 +11902,19 @@
         <v>71</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>71</v>
@@ -11918,7 +11963,7 @@
         <v>71</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>72</v>
@@ -11935,10 +11980,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12035,10 +12080,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12137,14 +12182,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12166,16 +12211,16 @@
         <v>123</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>71</v>
@@ -12224,7 +12269,7 @@
         <v>71</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>72</v>
@@ -12241,10 +12286,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12267,19 +12312,19 @@
         <v>71</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>71</v>
@@ -12304,31 +12349,31 @@
         <v>71</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>72</v>
@@ -12345,10 +12390,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12371,19 +12416,19 @@
         <v>71</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>71</v>
@@ -12432,7 +12477,7 @@
         <v>71</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>72</v>
@@ -12449,10 +12494,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12475,17 +12520,17 @@
         <v>71</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>396</v>
+        <v>510</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>71</v>
@@ -12522,7 +12567,7 @@
         <v>71</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="AC100" s="2"/>
       <c r="AD100" t="s" s="2">
@@ -12532,7 +12577,7 @@
         <v>129</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>72</v>
@@ -12544,18 +12589,18 @@
         <v>90</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>71</v>
@@ -12577,17 +12622,17 @@
         <v>71</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L101" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="M101" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>71</v>
@@ -12636,7 +12681,7 @@
         <v>71</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>72</v>
@@ -12653,10 +12698,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12753,10 +12798,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12855,13 +12900,13 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>122</v>
@@ -12883,10 +12928,10 @@
         <v>71</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>136</v>
@@ -12959,13 +13004,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>71</v>
@@ -12987,13 +13032,13 @@
         <v>71</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13061,10 +13106,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13161,10 +13206,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13263,13 +13308,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>71</v>
@@ -13294,12 +13339,14 @@
         <v>123</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>71</v>
@@ -13365,10 +13412,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13465,10 +13512,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13494,10 +13541,10 @@
         <v>123</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13565,10 +13612,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13608,7 +13655,7 @@
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>71</v>
@@ -13667,10 +13714,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13693,7 +13740,7 @@
         <v>71</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>164</v>
@@ -13765,13 +13812,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>71</v>
@@ -13793,7 +13840,7 @@
         <v>71</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>164</v>
@@ -13826,13 +13873,13 @@
         <v>71</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>71</v>
@@ -13867,10 +13914,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>138</v>
@@ -13898,12 +13945,14 @@
         <v>123</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>71</v>
@@ -13969,10 +14018,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14069,10 +14118,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14098,10 +14147,10 @@
         <v>123</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14169,10 +14218,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14271,10 +14320,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14371,13 +14420,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>71</v>
@@ -14402,12 +14451,14 @@
         <v>123</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>71</v>
@@ -14473,10 +14524,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14573,10 +14624,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14602,10 +14653,10 @@
         <v>123</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14673,10 +14724,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14716,7 +14767,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>71</v>
@@ -14775,10 +14826,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14875,13 +14926,13 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>71</v>
@@ -14906,12 +14957,14 @@
         <v>123</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N124" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>71</v>
@@ -14977,10 +15030,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15077,10 +15130,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15106,10 +15159,10 @@
         <v>123</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15177,10 +15230,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15220,7 +15273,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>71</v>
@@ -15279,10 +15332,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15379,13 +15432,13 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>71</v>
@@ -15410,12 +15463,14 @@
         <v>123</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>71</v>
@@ -15481,10 +15536,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15581,10 +15636,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15610,10 +15665,10 @@
         <v>123</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -15681,10 +15736,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15724,7 +15779,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>71</v>
@@ -15783,10 +15838,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15883,13 +15938,13 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>71</v>
@@ -15914,12 +15969,14 @@
         <v>123</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N134" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>71</v>
@@ -15985,10 +16042,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16085,10 +16142,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16114,10 +16171,10 @@
         <v>123</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -16185,10 +16242,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16228,7 +16285,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>71</v>
@@ -16287,10 +16344,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16313,7 +16370,7 @@
         <v>71</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>164</v>
@@ -16387,13 +16444,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>71</v>
@@ -16418,12 +16475,14 @@
         <v>123</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N139" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>71</v>
@@ -16489,10 +16548,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16589,10 +16648,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16618,10 +16677,10 @@
         <v>123</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -16689,10 +16748,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16732,7 +16791,7 @@
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="S142" t="s" s="2">
         <v>71</v>
@@ -16791,10 +16850,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16817,7 +16876,7 @@
         <v>71</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L143" t="s" s="2">
         <v>164</v>
@@ -16891,10 +16950,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16934,7 +16993,7 @@
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>71</v>
@@ -16993,10 +17052,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17019,7 +17078,7 @@
         <v>71</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="L145" t="s" s="2">
         <v>164</v>
@@ -17093,10 +17152,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17122,13 +17181,13 @@
         <v>99</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -17139,7 +17198,7 @@
         <v>71</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>71</v>
@@ -17154,13 +17213,13 @@
         <v>71</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>71</v>
@@ -17178,7 +17237,7 @@
         <v>71</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>72</v>
@@ -17187,7 +17246,7 @@
         <v>78</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>91</v>
@@ -17195,10 +17254,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17224,16 +17283,16 @@
         <v>146</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>71</v>
@@ -17282,7 +17341,7 @@
         <v>71</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>72</v>
@@ -17299,10 +17358,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17328,16 +17387,16 @@
         <v>99</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>71</v>
@@ -17362,13 +17421,13 @@
         <v>71</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>71</v>
@@ -17386,7 +17445,7 @@
         <v>71</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>72</v>
@@ -17403,10 +17462,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17429,16 +17488,16 @@
         <v>79</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -17488,7 +17547,7 @@
         <v>71</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>72</v>
@@ -17505,10 +17564,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17534,13 +17593,13 @@
         <v>163</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -17590,7 +17649,7 @@
         <v>71</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>72</v>
@@ -17602,15 +17661,15 @@
         <v>90</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17633,19 +17692,19 @@
         <v>71</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>71</v>
@@ -17694,7 +17753,7 @@
         <v>71</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>72</v>
@@ -17711,10 +17770,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17737,19 +17796,19 @@
         <v>71</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>71</v>
@@ -17798,7 +17857,7 @@
         <v>71</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>72</v>
@@ -17810,7 +17869,7 @@
         <v>90</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/ig/mc-changes/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T14:30:45+00:00</t>
+    <t>2023-05-09T15:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -574,7 +574,7 @@
 </t>
   </si>
   <si>
-    <t>Date d'ouverture de la structure</t>
+    <t>Date d'ouverture de la structure.</t>
   </si>
   <si>
     <t>The start of the period. The boundary is inclusive.</t>
@@ -596,7 +596,7 @@
     <t>Organization.extension.value[x].end</t>
   </si>
   <si>
-    <t>Date de fermeture de la structure</t>
+    <t>Date de fermeture de la structure.</t>
   </si>
   <si>
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
@@ -844,7 +844,7 @@
 </t>
   </si>
   <si>
-    <t>La ressource est-elle active? active | inactive</t>
+    <t>La ressource est-elle active? (active | inactive)</t>
   </si>
   <si>
     <t>Whether the organization's record is still in active use.</t>
@@ -1202,7 +1202,7 @@
     <t>statutJuridiqueINSEE</t>
   </si>
   <si>
-    <t>Statut juridique FINESS qui caracterise la situation juridique de la personne morale.</t>
+    <t>Statut juridique FINESS qui caractérise la situation juridique de la personne morale.</t>
   </si>
   <si>
     <t>Synonyme : statutJuridiqueINSEE</t>
@@ -1412,7 +1412,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">adresseEJ : Adresse géopostale de l'entité juridique ou adresseEG : Adresse(s) géopostale(s) de l'entité géographique </t>
+    <t>adresseEJ : Adresse géopostale de l'entité juridique ou adresseEG : Adresse(s) géopostale(s) de l'entité géographique.</t>
   </si>
   <si>
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>

--- a/ig/mc-changes/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization</t>
+    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:20:28+00:00</t>
+    <t>2023-05-09T16:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,7 +617,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-digital-certificate}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
 </t>
   </si>
   <si>
@@ -636,7 +636,7 @@
     <t>as-ext-organization-pharmacy-licence</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-organization-pharmacy-licence}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence}
 </t>
   </si>
   <si>
@@ -1408,7 +1408,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-address-extended}
+    <t xml:space="preserve">Address {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended}
 </t>
   </si>
   <si>
@@ -1431,7 +1431,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
@@ -1629,7 +1629,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-mailbox-mss}
+    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
 </t>
   </si>
   <si>
@@ -1654,7 +1654,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-mailbox-mss-metadata}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
 </t>
   </si>
   <si>
@@ -1883,7 +1883,7 @@
     <t>Organization.contact.telecom.extension.url</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-mailbox-mss-metadata</t>
+    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>

--- a/ig/mc-changes/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T16:25:19+00:00</t>
+    <t>2023-05-16T15:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
